--- a/outputs/horario_gerado.xlsx
+++ b/outputs/horario_gerado.xlsx
@@ -595,20 +595,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>GEO
+PROF GEO 3</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>POR
 PROF POR 1</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 3</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
+          <t>FTP
+PROF ADM 1</t>
         </is>
       </c>
     </row>
@@ -618,42 +618,42 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>FTP
 PROF ADM 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 1</t>
         </is>
       </c>
     </row>
@@ -661,14 +661,14 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
@@ -678,32 +678,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>ART
 PROF ART 2</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF ADM 1</t>
         </is>
       </c>
     </row>
@@ -712,14 +712,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 2</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -735,17 +735,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="B4:B5"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -813,8 +813,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 2</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -823,21 +823,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF MMD 1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>FIS
 PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
         </is>
       </c>
     </row>
@@ -845,15 +845,20 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -862,27 +867,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 1</t>
+          <t>MAT
+PROF MAT 3</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
         </is>
       </c>
     </row>
@@ -893,13 +893,8 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -913,17 +908,22 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
           <t>POR
 PROF POR 2</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>EDF
@@ -936,14 +936,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -958,15 +958,15 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E3:E6"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
@@ -1036,8 +1036,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 1</t>
+          <t>QUI
+PROF QUI 3</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1046,21 +1046,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>FTP
 PROF MMD 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
         </is>
       </c>
     </row>
@@ -1070,14 +1070,14 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -1085,24 +1085,24 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
           <t>FIS
 PROF FIS 1</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -1111,7 +1111,12 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -1120,14 +1125,14 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 2</t>
+          <t>MAT
+PROF MAT 3</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 2</t>
+          <t>EDF
+PROF EDF 3</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1138,8 +1143,8 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 3</t>
+          <t>MAT
+PROF MAT 3</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1153,12 +1158,7 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -1181,17 +1181,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F3:F6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1276,14 +1276,14 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>FIL
+PROF FIL 1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 3</t>
+          <t>MAT
+PROF MAT 3</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,7 @@
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
-        </is>
-      </c>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -1310,20 +1305,20 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>EDF
+PROF EDF 3</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>HIS
 PROF HIS 1</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>ART
 PROF ART 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 3</t>
         </is>
       </c>
     </row>
@@ -1333,19 +1328,19 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -1353,32 +1348,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 3</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 1</t>
+          <t>QUI
+PROF QUI 3</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 2</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>POR
+PROF POR 3</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1381,12 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
@@ -1404,17 +1404,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B3:B6"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1482,8 +1482,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 3</t>
+          <t>QUI
+PROF QUI 4</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1493,14 +1493,14 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 1</t>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
+          <t>GEO
+PROF GEO 2</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -1516,18 +1516,8 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -1536,27 +1526,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>FTP
+PROF MMD 2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>FIL
 PROF FIL 3</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 2</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>POR
+PROF POR 3</t>
         </is>
       </c>
     </row>
@@ -1564,9 +1554,9 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
@@ -1574,29 +1564,29 @@
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>BIO
 PROF BIO 2</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 3</t>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 4</t>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
     </row>
@@ -1604,16 +1594,26 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 3</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1627,17 +1627,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B8"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1705,31 +1705,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF MMD 2</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 3</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 4</t>
+          <t>POR
+PROF POR 3</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 4</t>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
     </row>
@@ -1737,34 +1737,39 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 4</t>
         </is>
       </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 4</t>
+          <t>FIL
+PROF FIL 3</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1779,13 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -1789,32 +1794,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>GEO
 PROF GEO 2</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
         </is>
       </c>
     </row>
@@ -1823,19 +1823,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -1850,17 +1850,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1939,20 +1939,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
           <t>MAT
 PROF MAT 4</t>
         </is>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 4</t>
+          <t>GEO
+PROF GEO 4</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1962,7 @@
       </c>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
@@ -1979,20 +1974,20 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
           <t>POR
 PROF POR 3</t>
         </is>
       </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 3</t>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
     </row>
@@ -2002,14 +1997,19 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>BIO
 PROF BIO 2</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -2017,32 +2017,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 1</t>
+          <t>MAT
+PROF MAT 4</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 3</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 4</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 4</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
         </is>
       </c>
     </row>
@@ -2050,13 +2050,13 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -2073,17 +2073,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2151,31 +2151,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>HIS
+PROF HIS 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>ART
 PROF ART 2</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 3</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 4</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
         </is>
       </c>
     </row>
@@ -2185,13 +2185,18 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>ING
 PROF ING 2</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -2200,22 +2205,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 1</t>
+          <t>GEO
+PROF GEO 4</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
+          <t>FTP
+PROF MMD 3</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>MAT
+PROF MAT 4</t>
         </is>
       </c>
     </row>
@@ -2223,19 +2233,9 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 4</t>
-        </is>
-      </c>
+      <c r="D6" s="5" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
@@ -2251,21 +2251,21 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 4</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
           <t>MAT
 PROF MAT 4</t>
         </is>
       </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 4</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
     </row>
@@ -2275,14 +2275,14 @@
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 4</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2296,17 +2296,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E3:E6"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2374,8 +2374,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 1</t>
+          <t>FIL
+PROF FIL 3</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -2385,20 +2385,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF MMD 3</t>
+          <t>EDF
+PROF EDF 4</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 4</t>
+          <t>MAT
+PROF MAT 4</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
     </row>
@@ -2406,16 +2406,16 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -2423,22 +2423,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>FTP
+PROF MMD 3</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 4</t>
+          <t>POR
+PROF POR 4</t>
         </is>
       </c>
     </row>
@@ -2448,19 +2453,19 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>ING
-PROF ING 2</t>
+          <t>SOC
+PROF SOC 2</t>
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 4</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -2468,29 +2473,24 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>GEO
+PROF GEO 4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 3</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -2499,13 +2499,13 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2519,17 +2519,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2597,8 +2597,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 2</t>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -2608,8 +2608,8 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 2</t>
+          <t>GEO
+PROF GEO 1</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2620,8 +2620,8 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
     </row>
@@ -2631,14 +2631,14 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 5</t>
+          <t>EDF
+PROF EDF 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
+          <t>FIL
+PROF FIL 2</t>
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 2</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
     </row>
@@ -2671,14 +2671,14 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 5</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -2686,49 +2686,49 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>FIS
+PROF FIS 2</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 2</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 5</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 5</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2745,14 +2745,14 @@
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E6"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F6:F7"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2820,31 +2820,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>FTP
+PROF TI 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 5</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF TI 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 2</t>
+          <t>MAT
+PROF MAT 5</t>
         </is>
       </c>
     </row>
@@ -2852,9 +2852,9 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
@@ -2862,18 +2862,18 @@
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
+      <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 2</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
+          <t>FIS
+PROF FIS 2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2889,13 +2889,13 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -2910,26 +2910,26 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 2</t>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 5</t>
+          <t>GEO
+PROF GEO 1</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>EDF
 PROF EDF 2</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
     </row>
@@ -2945,8 +2945,8 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>SOC
-PROF SOC 1</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
@@ -2965,17 +2965,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3043,8 +3043,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 1</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3054,20 +3054,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 1</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 1</t>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -3075,21 +3075,21 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -3097,27 +3097,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>GEO
 PROF GEO 3</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 1</t>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,12 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
@@ -3143,26 +3148,26 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF ADM 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
         </is>
       </c>
     </row>
@@ -3174,12 +3179,7 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3194,16 +3194,16 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3272,25 +3272,25 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 5</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF TI 1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 5</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 5</t>
+          <t>HIS
+PROF HIS 2</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -3304,34 +3304,39 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>FIL
+PROF FIL 2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
     </row>
@@ -3339,15 +3344,15 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -3356,27 +3361,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 2</t>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
+          <t>MAT
+PROF MAT 5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 1</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 2</t>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
     </row>
@@ -3384,26 +3394,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3417,17 +3417,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D3:D6"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3495,8 +3495,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>HIS
+PROF HIS 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3518,8 +3518,8 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 2</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
     </row>
@@ -3527,16 +3527,16 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>FIL
+PROF FIL 4</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>ART
 PROF ART 1</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 2</t>
+          <t>POR
+PROF POR 6</t>
         </is>
       </c>
     </row>
@@ -3567,17 +3567,12 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
         </is>
       </c>
       <c r="E6" s="6" t="n"/>
@@ -3589,17 +3584,22 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 4</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
           <t>GEO
 PROF GEO 3</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 2</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>MAT
@@ -3608,8 +3608,8 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 6</t>
+          <t>FIS
+PROF FIS 2</t>
         </is>
       </c>
     </row>
@@ -3618,13 +3618,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 6</t>
         </is>
       </c>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
@@ -3640,17 +3640,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E3:E6"/>
     <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3718,8 +3718,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 2</t>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3728,21 +3728,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 4</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 6</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 6</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF TI 2</t>
         </is>
       </c>
     </row>
@@ -3750,11 +3750,16 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -3762,37 +3767,42 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 6</t>
+          <t>FTP
+PROF TI 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 2</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 6</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 2</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
+      <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 2</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t>SOC
@@ -3805,34 +3815,24 @@
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 4</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+          <t>MAT
+PROF MAT 6</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 3</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>EDF
+PROF EDF 2</t>
         </is>
       </c>
     </row>
@@ -3842,13 +3842,13 @@
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -3863,17 +3863,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B8"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D6:D7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3941,31 +3941,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>FIL
+PROF FIL 4</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>ART
 PROF ART 1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF TI 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 2</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>MAT
+PROF MAT 6</t>
         </is>
       </c>
     </row>
@@ -3973,15 +3973,20 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -3990,22 +3995,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 2</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
           <t>GEO
 PROF GEO 3</t>
         </is>
       </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF TI 2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 6</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 6</t>
+          <t>EDF
+PROF EDF 2</t>
         </is>
       </c>
     </row>
@@ -4013,14 +4023,9 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="5" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
@@ -4030,32 +4035,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 6</t>
+          <t>HIS
+PROF HIS 2</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 6</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 4</t>
-        </is>
-      </c>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
       <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>QUI
 PROF QUI 2</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
         </is>
       </c>
     </row>
@@ -4063,15 +4063,15 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 6</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -4087,16 +4087,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="D7:D8"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4164,31 +4164,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>GEO
+PROF GEO 3</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF ADM 1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>POR
+PROF POR 1</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,12 @@
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4208,27 +4213,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF ADM 1</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 3</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -4241,8 +4246,8 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>SOC
-PROF SOC 2</t>
+          <t>ING
+PROF ING 2</t>
         </is>
       </c>
       <c r="F6" s="6" t="n"/>
@@ -4253,32 +4258,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 1</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
     </row>
@@ -4286,21 +4291,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 1</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4318,11 +4318,11 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
@@ -4393,31 +4393,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>HIS
 PROF HIS 2</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 2</t>
+          <t>FTP
+PROF GSD 1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
     </row>
@@ -4425,17 +4425,12 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
         </is>
       </c>
       <c r="E4" s="6" t="n"/>
@@ -4447,27 +4442,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF GSD 1</t>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF GSD 1</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
           <t>FIL
 PROF FIL 3</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4473,7 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -4492,32 +4482,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>FIS
 PROF FIS 2</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 2</t>
+          <t>FTP
+PROF GSD 1</t>
         </is>
       </c>
     </row>
@@ -4525,8 +4515,18 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -4543,14 +4543,14 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
@@ -4622,31 +4622,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF IA 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
           <t>MAT
 PROF MAT 7</t>
         </is>
       </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 4</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
     </row>
@@ -4656,9 +4656,14 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF IA 1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4666,24 +4671,24 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
           <t>POR
 PROF POR 1</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 4</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -4693,12 +4698,7 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -4706,16 +4706,16 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
           <t>EDF
 PROF EDF 3</t>
         </is>
       </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 7</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>ART
@@ -4724,16 +4724,11 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 1</t>
-        </is>
-      </c>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -4747,11 +4742,16 @@
 PROF ING 2</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>POR
+PROF POR 1</t>
         </is>
       </c>
     </row>
@@ -4768,16 +4768,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F4:F7"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4845,31 +4845,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 7</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF IA 1</t>
+          <t>GEO
+PROF GEO 1</t>
         </is>
       </c>
     </row>
@@ -4880,13 +4880,8 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4894,61 +4889,66 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>POR
+PROF POR 4</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 1</t>
+          <t>FTP
+PROF IA 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 7</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="5" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
+      <c r="B7" s="6" t="n"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>EDF
 PROF EDF 3</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -4962,20 +4962,20 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>BIO
 PROF BIO 1</t>
         </is>
       </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -4991,16 +4991,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F3:F6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D5:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5068,8 +5068,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF IA 1</t>
+          <t>GEO
+PROF GEO 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5078,21 +5078,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 4</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>EDF
 PROF EDF 3</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
         </is>
       </c>
     </row>
@@ -5100,39 +5100,39 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>MAT
+PROF MAT 7</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 1</t>
+          <t>FTP
+PROF IA 1</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 4</t>
+          <t>MAT
+PROF MAT 7</t>
         </is>
       </c>
     </row>
@@ -5140,15 +5140,15 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -5157,32 +5157,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 7</t>
+          <t>FIL
+PROF FIL 4</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>FIS
 PROF FIS 3</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 3</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
     </row>
@@ -5192,14 +5187,19 @@
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5213,17 +5213,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B3:B6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5291,8 +5291,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 2</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5301,21 +5301,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>ART
 PROF ART 2</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 1</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 2</t>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
     </row>
@@ -5325,14 +5325,19 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 2</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -5340,15 +5345,15 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 4</t>
+          <t>MAT
+PROF MAT 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 2</t>
+          <t>FTP
+PROF PUB 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5359,8 +5364,8 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>FIL
+PROF FIL 1</t>
         </is>
       </c>
     </row>
@@ -5380,32 +5385,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF PUB 1</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF PUB 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
+          <t>GEO
+PROF GEO 4</t>
         </is>
       </c>
     </row>
@@ -5413,20 +5418,15 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -5444,11 +5444,11 @@
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
@@ -5520,8 +5520,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF PUB 1</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5537,14 +5537,14 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
+          <t>FIL
+PROF FIL 1</t>
         </is>
       </c>
     </row>
@@ -5552,15 +5552,15 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -5569,27 +5569,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF PUB 1</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 4</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
         </is>
       </c>
     </row>
@@ -5601,8 +5601,8 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SOC
-PROF SOC 1</t>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
       <c r="E6" s="6" t="n"/>
@@ -5614,8 +5614,8 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>FTP
+PROF PUB 1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -5624,22 +5624,17 @@
 PROF MAT 2</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 1</t>
-        </is>
-      </c>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
     </row>
@@ -5647,16 +5642,21 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5671,16 +5671,16 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/horario_gerado.xlsx
+++ b/outputs/horario_gerado.xlsx
@@ -595,14 +595,14 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>GEO
 PROF GEO 3</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -618,8 +618,8 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -631,29 +631,24 @@
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
+          <t>POR
+PROF POR 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 1</t>
+          <t>FIL
+PROF FIL 2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF ADM 1</t>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
     </row>
@@ -661,14 +656,14 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
@@ -676,34 +671,29 @@
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
-        </is>
-      </c>
+      <c r="B7" s="6" t="n"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>FTP
+PROF ADM 1</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>ART
 PROF ART 2</t>
         </is>
       </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 1</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
     </row>
@@ -711,13 +701,23 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 2</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
         </is>
       </c>
       <c r="F8" s="6" t="n"/>
@@ -735,17 +735,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B4:B5"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -813,8 +813,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>POR
+PROF POR 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -823,21 +823,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 3</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>HIS
 PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
         </is>
       </c>
     </row>
@@ -847,42 +847,42 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 2</t>
+          <t>QUI
+PROF QUI 3</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 2</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF MMD 1</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 3</t>
+          <t>FIL
+PROF FIL 1</t>
         </is>
       </c>
     </row>
@@ -890,10 +890,20 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -902,8 +912,8 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 3</t>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -914,20 +924,15 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 3</t>
+          <t>GEO
+PROF GEO 2</t>
         </is>
       </c>
     </row>
@@ -938,12 +943,7 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -958,17 +958,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B4:B5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1036,31 +1036,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
           <t>FTP
 PROF MMD 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
     </row>
@@ -1068,41 +1068,41 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
+      <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 1</t>
+          <t>GEO
+PROF GEO 2</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -1111,12 +1111,7 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -1149,8 +1144,8 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 2</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1162,12 @@
         </is>
       </c>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1181,16 +1181,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1259,31 +1259,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF MMD 1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
         </is>
       </c>
     </row>
@@ -1291,36 +1291,41 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 3</t>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
+          <t>FIL
+PROF FIL 1</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -1329,18 +1334,8 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -1348,20 +1343,20 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 3</t>
+          <t>POR
+PROF POR 3</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>EDF
+PROF EDF 3</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1372,8 +1367,8 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 3</t>
+          <t>MAT
+PROF MAT 3</t>
         </is>
       </c>
     </row>
@@ -1383,11 +1378,16 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 3</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n"/>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -1404,16 +1404,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1493,8 +1493,8 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1505,8 +1505,8 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 4</t>
+          <t>MAT
+PROF MAT 3</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,12 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
@@ -1526,27 +1531,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF MMD 2</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 3</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
         </is>
       </c>
     </row>
@@ -1554,17 +1559,27 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>MAT
@@ -1573,22 +1588,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>POR
+PROF POR 3</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
+          <t>FIL
+PROF FIL 3</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -1598,22 +1608,12 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 3</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1627,16 +1627,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F5:F8"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1705,8 +1705,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 3</t>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>FTP
 PROF MMD 2</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 1</t>
+          <t>MAT
+PROF MAT 4</t>
         </is>
       </c>
     </row>
@@ -1739,19 +1739,14 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -1759,17 +1754,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 4</t>
+          <t>QUI
+PROF QUI 4</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 3</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,7 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -1794,27 +1789,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>EDF
 PROF EDF 4</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 4</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 2</t>
         </is>
       </c>
     </row>
@@ -1823,17 +1823,17 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
         </is>
       </c>
       <c r="F8" s="6" t="n"/>
@@ -1852,15 +1852,15 @@
   <mergeCells count="11">
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E4:E5"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1928,8 +1928,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF MMD 3</t>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1939,20 +1939,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 4</t>
+          <t>POR
+PROF POR 3</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>QUI
+PROF QUI 4</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 4</t>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
     </row>
@@ -1960,34 +1960,49 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 3</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 3</t>
+          <t>FTP
+PROF MMD 3</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 4</t>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 1</t>
+          <t>EDF
+PROF EDF 4</t>
         </is>
       </c>
     </row>
@@ -1997,19 +2012,9 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
+      <c r="D6" s="5" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -2017,32 +2022,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>GEO
+PROF GEO 4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 4</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="n"/>
       <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 3</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 3</t>
         </is>
       </c>
     </row>
@@ -2051,15 +2051,15 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2077,13 +2077,13 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2151,8 +2151,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 1</t>
+          <t>MAT
+PROF MAT 4</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -2162,8 +2162,8 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>MAT
+PROF MAT 4</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2174,8 +2174,8 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 4</t>
+          <t>GEO
+PROF GEO 4</t>
         </is>
       </c>
     </row>
@@ -2183,20 +2183,15 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -2205,27 +2200,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 4</t>
+          <t>POR
+PROF POR 4</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF MMD 3</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 4</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 4</t>
+          <t>FIL
+PROF FIL 3</t>
         </is>
       </c>
     </row>
@@ -2235,8 +2230,8 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -2245,27 +2240,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 3</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>FIS
 PROF FIS 3</t>
         </is>
       </c>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
     </row>
@@ -2273,14 +2268,19 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 4</t>
+          <t>SOC
+PROF SOC 2</t>
         </is>
       </c>
     </row>
@@ -2296,17 +2296,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E5:E8"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2374,31 +2374,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>FTP
+PROF MMD 3</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>FIL
 PROF FIL 3</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 4</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
         </is>
       </c>
     </row>
@@ -2406,44 +2406,34 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>HIS
 PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 4</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 3</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
         </is>
       </c>
     </row>
@@ -2451,19 +2441,14 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
         </is>
       </c>
     </row>
@@ -2473,39 +2458,54 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>GEO
 PROF GEO 4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>BIO
 PROF BIO 2</t>
         </is>
       </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2519,16 +2519,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2597,31 +2597,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
           <t>FTP
 PROF TI 1</t>
         </is>
       </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 5</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
     </row>
@@ -2629,14 +2629,14 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ING
-PROF ING 1</t>
+          <t>FIS
+PROF FIS 2</t>
         </is>
       </c>
     </row>
@@ -2644,26 +2644,21 @@
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 2</t>
-        </is>
-      </c>
+      <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -2675,8 +2670,8 @@
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 5</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
     </row>
@@ -2686,26 +2681,26 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>MAT
+PROF MAT 5</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 2</t>
+          <t>EDF
+PROF EDF 2</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>HIS
 PROF HIS 2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 5</t>
         </is>
       </c>
       <c r="F7" s="6" t="n"/>
@@ -2718,11 +2713,16 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
           <t>SOC
 PROF SOC 1</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>POR
@@ -2742,16 +2742,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2820,8 +2820,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF TI 1</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -2831,8 +2831,8 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 2</t>
+          <t>GEO
+PROF GEO 1</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2852,7 +2852,12 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
@@ -2862,7 +2867,12 @@
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -2872,14 +2882,14 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
+          <t>FTP
+PROF TI 1</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2897,12 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -2896,7 +2911,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -2904,8 +2919,8 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
+          <t>EDF
+PROF EDF 2</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2916,39 +2931,24 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 1</t>
+          <t>FIL
+PROF FIL 2</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -2969,13 +2969,13 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F5:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3043,8 +3043,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>MAT
+PROF MAT 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3054,20 +3054,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
+          <t>FIL
+PROF FIL 2</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>POR
+PROF POR 1</t>
         </is>
       </c>
     </row>
@@ -3075,18 +3075,13 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 1</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>SOC
-PROF SOC 2</t>
+          <t>ING
+PROF ING 2</t>
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
@@ -3097,27 +3092,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>FTP
+PROF ADM 1</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 1</t>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 3</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>FIS
 PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -3125,14 +3120,14 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
@@ -3142,8 +3137,8 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF ADM 1</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3154,14 +3149,14 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 1</t>
+          <t>GEO
+PROF GEO 3</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 2</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -3175,7 +3170,12 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
@@ -3194,17 +3194,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3283,14 +3283,14 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>HIS
+PROF HIS 2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF TI 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 2</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -3306,13 +3306,13 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 1</t>
         </is>
       </c>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -3321,22 +3321,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 2</t>
         </is>
       </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 2</t>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
     </row>
@@ -3344,16 +3344,16 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -3361,32 +3361,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 5</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>POR
 PROF POR 5</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 5</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
+          <t>ING
+PROF ING 1</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D6"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E3:E6"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3506,20 +3506,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 6</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
           <t>FTP
 PROF TI 2</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>QUI
 PROF QUI 2</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
         </is>
       </c>
     </row>
@@ -3534,8 +3534,8 @@
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 4</t>
+          <t>GEO
+PROF GEO 3</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 6</t>
+          <t>EDF
+PROF EDF 2</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,7 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
@@ -3584,22 +3579,22 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 3</t>
+          <t>FIL
+PROF FIL 4</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>BIO
 PROF BIO 1</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 2</t>
-        </is>
-      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>MAT
@@ -3608,8 +3603,8 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>MAT
+PROF MAT 6</t>
         </is>
       </c>
     </row>
@@ -3620,11 +3615,16 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>POR
 PROF POR 6</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
@@ -3640,16 +3640,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="D3:D6"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3729,20 +3729,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 4</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
           <t>POR
 PROF POR 6</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 3</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,12 @@
       </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF TI 2</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -3767,27 +3772,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF TI 2</t>
+          <t>EDF
+PROF EDF 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 2</t>
-        </is>
-      </c>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 6</t>
+          <t>FIL
+PROF FIL 4</t>
         </is>
       </c>
     </row>
@@ -3795,44 +3795,39 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 6</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 3</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 6</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 2</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 2</t>
+          <t>HIS
+PROF HIS 2</t>
         </is>
       </c>
     </row>
@@ -3842,14 +3837,19 @@
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 6</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3863,17 +3863,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="E4:E7"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3941,31 +3941,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 6</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 6</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 2</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>FIL
 PROF FIL 4</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 6</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 6</t>
         </is>
       </c>
     </row>
@@ -3975,18 +3975,8 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -3995,27 +3985,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 3</t>
+          <t>FTP
+PROF TI 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF TI 2</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 6</t>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 2</t>
+          <t>HIS
+PROF HIS 2</t>
         </is>
       </c>
     </row>
@@ -4023,39 +4013,49 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 2</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>FIS
 PROF FIS 2</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n"/>
       <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 6</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 3</t>
         </is>
       </c>
     </row>
@@ -4063,15 +4063,15 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -4086,17 +4086,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B5:B8"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4164,8 +4164,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 3</t>
+          <t>FIL
+PROF FIL 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF ADM 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 1</t>
         </is>
       </c>
     </row>
@@ -4199,13 +4199,13 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4213,27 +4213,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 2</t>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF ADM 1</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>POR
+PROF POR 1</t>
         </is>
       </c>
     </row>
@@ -4241,13 +4236,18 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>ING
-PROF ING 2</t>
+          <t>FTP
+PROF ADM 1</t>
         </is>
       </c>
       <c r="F6" s="6" t="n"/>
@@ -4258,32 +4258,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
+          <t>GEO
+PROF GEO 3</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 1</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 1</t>
-        </is>
-      </c>
+          <t>FTP
+PROF ADM 1</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
     </row>
@@ -4291,16 +4286,21 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4316,15 +4316,15 @@
   <mergeCells count="12">
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4393,8 +4393,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 2</t>
+          <t>FIL
+PROF FIL 3</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4404,20 +4404,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 2</t>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF GSD 1</t>
+          <t>FIS
+PROF FIS 2</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
     </row>
@@ -4427,14 +4427,14 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4442,27 +4442,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
+          <t>HIS
+PROF HIS 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 3</t>
+          <t>FTP
+PROF GSD 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 2</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
     </row>
@@ -4470,11 +4470,21 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -4482,32 +4492,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
           <t>GEO
 PROF GEO 2</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>FTP
 PROF GSD 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -4515,18 +4525,8 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -4548,12 +4548,12 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4639,14 +4639,14 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 1</t>
+          <t>FIL
+PROF FIL 4</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>MAT
+PROF MAT 7</t>
         </is>
       </c>
     </row>
@@ -4658,12 +4658,7 @@
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF IA 1</t>
-        </is>
-      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4678,17 +4673,22 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 3</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 4</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF IA 1</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -4696,8 +4696,18 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -4712,48 +4722,38 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
           <t>ART
 PROF ART 2</t>
         </is>
       </c>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 2</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 1</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4767,17 +4767,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F4:F7"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F5:F8"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4845,31 +4845,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>EDF
+PROF EDF 3</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF IA 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>FIS
 PROF FIS 3</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 1</t>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
     </row>
@@ -4879,9 +4879,14 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4889,27 +4894,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 4</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF IA 1</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 4</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
+          <t>GEO
+PROF GEO 1</t>
         </is>
       </c>
     </row>
@@ -4919,38 +4919,43 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 7</t>
+          <t>ING
+PROF ING 2</t>
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 3</t>
-        </is>
-      </c>
+          <t>MAT
+PROF MAT 7</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 7</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>FIL
@@ -4962,20 +4967,15 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -4990,17 +4990,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5068,8 +5068,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 1</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5079,20 +5079,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 3</t>
+          <t>FIL
+PROF FIL 4</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF IA 1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>QUI
 PROF QUI 3</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
         </is>
       </c>
     </row>
@@ -5100,10 +5100,15 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -5112,27 +5117,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
+          <t>EDF
+PROF EDF 3</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF IA 1</t>
-        </is>
-      </c>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 7</t>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
     </row>
@@ -5140,15 +5140,10 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -5157,27 +5152,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 4</t>
+          <t>MAT
+PROF MAT 7</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>BIO
 PROF BIO 1</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 7</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>POR
+PROF POR 4</t>
         </is>
       </c>
     </row>
@@ -5186,20 +5186,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 4</t>
         </is>
       </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5213,16 +5213,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5291,31 +5291,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>FIL
+PROF FIL 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>EDF
 PROF EDF 1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
         </is>
       </c>
     </row>
@@ -5326,16 +5326,11 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>SOC
-PROF SOC 1</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
     </row>
@@ -5345,27 +5340,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>GEO
+PROF GEO 4</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 2</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF PUB 1</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 1</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5371,12 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -5385,32 +5385,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF PUB 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF PUB 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>POR
 PROF POR 2</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF PUB 1</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 4</t>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
     </row>
@@ -5420,8 +5420,8 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>SOC
+PROF SOC 1</t>
         </is>
       </c>
       <c r="C8" s="6" t="n"/>
@@ -5441,9 +5441,9 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
@@ -5520,8 +5520,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5530,21 +5530,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 1</t>
         </is>
       </c>
     </row>
@@ -5552,15 +5552,20 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -5569,27 +5574,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 2</t>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>ING
+PROF ING 2</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 4</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>FTP
 PROF PUB 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 4</t>
         </is>
       </c>
     </row>
@@ -5601,8 +5606,8 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
       <c r="E6" s="6" t="n"/>
@@ -5614,27 +5619,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 1</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF PUB 1</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 2</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
         </is>
       </c>
     </row>
@@ -5651,12 +5656,7 @@
         </is>
       </c>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5671,14 +5671,14 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="B5:B6"/>

--- a/outputs/horario_gerado.xlsx
+++ b/outputs/horario_gerado.xlsx
@@ -595,20 +595,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>GEO
+PROF GEO 3</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 3</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF ADM 1</t>
         </is>
       </c>
     </row>
@@ -618,8 +618,8 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -631,24 +631,29 @@
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF ADM 1</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>POR
 PROF POR 1</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
     </row>
@@ -656,12 +661,7 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 1</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
@@ -671,29 +671,34 @@
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>FTP
 PROF ADM 1</t>
         </is>
       </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>ART
 PROF ART 2</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
     </row>
@@ -701,23 +706,18 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
           <t>ING
 PROF ING 2</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
         </is>
       </c>
       <c r="F8" s="6" t="n"/>
@@ -735,16 +735,16 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="B4:B5"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -813,8 +813,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 2</t>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -824,20 +824,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 3</t>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
         </is>
       </c>
     </row>
@@ -847,42 +847,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 3</t>
+          <t>ING
+PROF ING 1</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF MMD 1</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 3</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
           <t>FIL
 PROF FIL 1</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
     </row>
@@ -890,19 +895,9 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
@@ -912,27 +907,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
           <t>POR
 PROF POR 2</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 3</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
         </is>
       </c>
     </row>
@@ -943,7 +938,12 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -958,17 +958,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E4:E7"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1036,8 +1036,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF MMD 1</t>
+          <t>GEO
+PROF GEO 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 1</t>
+          <t>MAT
+PROF MAT 3</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
+          <t>MAT
+PROF MAT 3</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
     </row>
@@ -1068,51 +1068,61 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF MMD 1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 1</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
           <t>QUI
 PROF QUI 3</t>
         </is>
       </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -1120,34 +1130,29 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 3</t>
+          <t>FIL
+PROF FIL 1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>EDF
 PROF EDF 3</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -1155,12 +1160,7 @@
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B3:B6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1270,20 +1270,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>FTP
+PROF MMD 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>QUI
 PROF QUI 3</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF MMD 1</t>
+          <t>FIL
+PROF FIL 1</t>
         </is>
       </c>
     </row>
@@ -1293,14 +1293,9 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -1313,19 +1308,19 @@
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>FIS
 PROF FIS 1</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 1</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -1349,26 +1344,26 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>EDF
+PROF EDF 3</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>POR
 PROF POR 3</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 3</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 2</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 3</t>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
     </row>
@@ -1382,15 +1377,20 @@
 PROF ING 1</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>BIO
 PROF BIO 1</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1405,16 +1405,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F3:F6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D6"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1482,8 +1482,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 4</t>
+          <t>FTP
+PROF MMD 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>ART
 PROF ART 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 2</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
         </is>
       </c>
     </row>
@@ -1514,44 +1514,39 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
+      <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 4</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
           <t>HIS
 PROF HIS 1</t>
         </is>
       </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF MMD 2</t>
+          <t>POR
+PROF POR 3</t>
         </is>
       </c>
     </row>
@@ -1561,14 +1556,14 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -1576,42 +1571,47 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>POR
 PROF POR 3</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 3</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 3</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 3</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>BIO
 PROF BIO 2</t>
         </is>
       </c>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
@@ -1627,17 +1627,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F5:F8"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1705,8 +1705,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 1</t>
+          <t>QUI
+PROF QUI 4</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF MMD 2</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>HIS
 PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 2</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
         </is>
       </c>
     </row>
@@ -1741,12 +1741,17 @@
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -1754,22 +1759,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 4</t>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>FIL
 PROF FIL 3</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
         </is>
       </c>
     </row>
@@ -1789,32 +1794,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 4</t>
         </is>
       </c>
     </row>
@@ -1822,20 +1827,15 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 3</t>
         </is>
       </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -1853,10 +1853,10 @@
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E3:E6"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
@@ -1928,31 +1928,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
           <t>POR
 PROF POR 3</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>QUI
 PROF QUI 4</t>
         </is>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
+          <t>FIL
+PROF FIL 3</t>
         </is>
       </c>
     </row>
@@ -1960,21 +1960,11 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -1982,27 +1972,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 3</t>
+          <t>EDF
+PROF EDF 4</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF MMD 3</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 4</t>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
     </row>
@@ -2012,9 +2002,14 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -2022,27 +2017,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>GEO
 PROF GEO 4</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
         </is>
       </c>
     </row>
@@ -2051,15 +2046,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2073,17 +2073,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E5:E8"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2162,20 +2162,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 4</t>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 4</t>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 4</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
     </row>
@@ -2188,11 +2188,16 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n"/>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -2213,14 +2218,14 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>GEO
+PROF GEO 4</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF MMD 3</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 3</t>
         </is>
       </c>
     </row>
@@ -2231,8 +2236,8 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -2240,49 +2245,44 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
           <t>ART
 PROF ART 2</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 4</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 3</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 2</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2296,15 +2296,15 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="F5:F8"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
@@ -2374,8 +2374,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF MMD 3</t>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -2384,21 +2384,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 4</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 4</t>
         </is>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 4</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 3</t>
+          <t>EDF
+PROF EDF 4</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
@@ -2416,24 +2416,29 @@
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>FTP
+PROF MMD 3</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 3</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 4</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
         </is>
       </c>
     </row>
@@ -2441,49 +2446,39 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="5" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 4</t>
-        </is>
-      </c>
+      <c r="B7" s="6" t="n"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 1</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 4</t>
         </is>
       </c>
     </row>
@@ -2491,18 +2486,23 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>ING
+PROF ING 2</t>
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>ING
-PROF ING 2</t>
+          <t>SOC
+PROF SOC 2</t>
         </is>
       </c>
       <c r="F8" s="6" t="n"/>
@@ -2520,16 +2520,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D5:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2597,31 +2597,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF TI 1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
           <t>MAT
 PROF MAT 5</t>
         </is>
       </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 2</t>
+          <t>MAT
+PROF MAT 5</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>HIS
+PROF HIS 2</t>
         </is>
       </c>
     </row>
@@ -2629,14 +2629,14 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>SOC
+PROF SOC 1</t>
         </is>
       </c>
     </row>
@@ -2644,36 +2644,51 @@
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
+          <t>FTP
+PROF TI 1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>QUI
 PROF QUI 2</t>
         </is>
       </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -2681,29 +2696,24 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 5</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
           <t>EDF
 PROF EDF 2</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 2</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -2713,22 +2723,12 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
           <t>POR
 PROF POR 5</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2742,17 +2742,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B3:B6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D6:D7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2820,8 +2820,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 5</t>
         </is>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 2</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 5</t>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
     </row>
@@ -2852,16 +2852,21 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -2869,27 +2874,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF TI 1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>ART
 PROF ART 1</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF TI 1</t>
         </is>
       </c>
     </row>
@@ -2897,21 +2902,16 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -2919,29 +2919,29 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>QUI
+PROF QUI 2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 5</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>EDF
 PROF EDF 2</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -2966,16 +2966,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3043,31 +3043,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>MAT
+PROF MAT 1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 1</t>
+          <t>FTP
+PROF ADM 1</t>
         </is>
       </c>
     </row>
@@ -3075,15 +3075,15 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -3092,27 +3092,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF ADM 1</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>POR
+PROF POR 1</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,7 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
@@ -3137,32 +3132,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>GEO
+PROF GEO 3</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>BIO
 PROF BIO 2</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 3</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF ADM 1</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
     </row>
@@ -3170,16 +3165,21 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3194,17 +3194,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3272,8 +3272,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 5</t>
+          <t>EDF
+PROF EDF 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3283,20 +3283,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 2</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>FTP
 PROF TI 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 2</t>
         </is>
       </c>
     </row>
@@ -3306,14 +3306,9 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -3321,24 +3316,24 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 2</t>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 2</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -3347,13 +3342,13 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -3361,32 +3356,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
           <t>MAT
 PROF MAT 5</t>
         </is>
       </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 1</t>
+          <t>MAT
+PROF MAT 5</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 5</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3390,12 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="3" t="inlineStr">
@@ -3417,15 +3417,15 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="F3:F6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E3:E6"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
@@ -3506,20 +3506,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF TI 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
           <t>POR
 PROF POR 6</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 6</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,12 @@
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF TI 2</t>
+        </is>
+      </c>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
@@ -3552,8 +3557,8 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -3569,7 +3574,7 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="5" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
@@ -3585,26 +3590,21 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 6</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>ART
 PROF ART 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 6</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 6</t>
         </is>
       </c>
     </row>
@@ -3613,20 +3613,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 6</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3641,14 +3641,14 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="D4:D7"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
   </mergeCells>
@@ -3718,25 +3718,25 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
           <t>POR
 PROF POR 6</t>
         </is>
       </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 6</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>FTP
+PROF TI 2</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -3752,18 +3752,13 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ING
-PROF ING 1</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF TI 2</t>
-        </is>
-      </c>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -3772,15 +3767,15 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 2</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
@@ -3797,8 +3792,13 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -3807,23 +3807,28 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 2</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 6</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 6</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>HIS
@@ -3838,12 +3843,7 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 6</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>SOC
@@ -3863,17 +3863,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3952,20 +3952,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>FIL
+PROF FIL 4</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 6</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 2</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 4</t>
+          <t>FIS
+PROF FIS 2</t>
         </is>
       </c>
     </row>
@@ -3992,20 +3992,20 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 2</t>
+          <t>GEO
+PROF GEO 3</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 1</t>
+          <t>EDF
+PROF EDF 2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 2</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
     </row>
@@ -4016,16 +4016,11 @@
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>SOC
-PROF SOC 1</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
     </row>
@@ -4042,22 +4037,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>HIS
+PROF HIS 2</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 6</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 3</t>
-        </is>
-      </c>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -4065,14 +4055,24 @@
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4087,15 +4087,15 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="B5:B8"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F6:F7"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4164,31 +4164,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>FTP
+PROF ADM 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>FIL
 PROF FIL 2</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 1</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 1</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -4199,12 +4199,7 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 1</t>
-        </is>
-      </c>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -4213,22 +4208,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>HIS
 PROF HIS 3</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 1</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
     </row>
@@ -4236,21 +4236,21 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF ADM 1</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -4258,27 +4258,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>POR
+PROF POR 1</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>FTP
+PROF ADM 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>GEO
 PROF GEO 3</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF ADM 1</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
     </row>
@@ -4289,16 +4294,11 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>ING
-PROF ING 2</t>
+          <t>POR
+PROF POR 1</t>
         </is>
       </c>
     </row>
@@ -4316,15 +4316,15 @@
   <mergeCells count="12">
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4404,20 +4404,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
+          <t>MAT
+PROF MAT 2</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
     </row>
@@ -4431,8 +4431,8 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
+          <t>ING
+PROF ING 2</t>
         </is>
       </c>
     </row>
@@ -4455,14 +4455,14 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
+          <t>FIS
+PROF FIS 2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,7 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -4504,20 +4499,20 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4522,12 @@
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
@@ -4551,9 +4551,9 @@
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4622,21 +4622,21 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 7</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>FIL
@@ -4645,8 +4645,8 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 7</t>
+          <t>FTP
+PROF IA 1</t>
         </is>
       </c>
     </row>
@@ -4654,11 +4654,16 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4666,29 +4671,24 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 1</t>
+          <t>QUI
+PROF QUI 3</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF IA 1</t>
-        </is>
-      </c>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -4698,17 +4698,12 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n"/>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -4716,43 +4711,48 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 7</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>EDF
 PROF EDF 3</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 1</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -4767,16 +4767,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F3:F6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F5:F8"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4856,20 +4856,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>FTP
 PROF IA 1</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
+          <t>MAT
+PROF MAT 7</t>
         </is>
       </c>
     </row>
@@ -4879,14 +4879,14 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 1</t>
         </is>
       </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4899,17 +4899,17 @@
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
         </is>
       </c>
     </row>
@@ -4925,12 +4925,7 @@
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -4939,27 +4934,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>MAT
+PROF MAT 7</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>POR
 PROF POR 4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
       <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 4</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
     </row>
@@ -4968,14 +4968,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
@@ -4992,15 +4992,15 @@
   <mergeCells count="11">
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D6"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5068,25 +5068,25 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
           <t>FIL
 PROF FIL 4</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>FTP
 PROF IA 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 3</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5100,15 +5100,10 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -5117,18 +5112,18 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 3</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
           <t>GEO
 PROF GEO 1</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>FIS
@@ -5143,7 +5138,12 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -5152,20 +5152,20 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5185,19 +5185,19 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
           <t>POR
 PROF POR 4</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
@@ -5213,17 +5213,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5291,8 +5291,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 1</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5302,20 +5302,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 2</t>
+          <t>FTP
+PROF PUB 1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 2</t>
+          <t>GEO
+PROF GEO 4</t>
         </is>
       </c>
     </row>
@@ -5323,16 +5323,21 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -5340,27 +5345,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 4</t>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 2</t>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ART
-PROF ART 2</t>
+          <t>POR
+PROF POR 2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
     </row>
@@ -5371,13 +5376,13 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -5385,32 +5390,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>FTP
 PROF PUB 1</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF PUB 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>FIL
+PROF FIL 1</t>
         </is>
       </c>
     </row>
@@ -5418,12 +5423,7 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
@@ -5441,16 +5441,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
@@ -5520,8 +5520,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 1</t>
+          <t>FTP
+PROF PUB 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5531,14 +5531,14 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 2</t>
+          <t>FIL
+PROF FIL 1</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 3</t>
+          <t>MAT
+PROF MAT 2</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5554,18 +5554,8 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -5574,27 +5564,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>POR
+PROF POR 2</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>ING
-PROF ING 2</t>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 4</t>
+          <t>QUI
+PROF QUI 1</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF PUB 1</t>
+          <t>POR
+PROF POR 2</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5592,17 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 1</t>
+          <t>SOC
+PROF SOC 1</t>
         </is>
       </c>
       <c r="E6" s="6" t="n"/>
@@ -5619,27 +5614,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 2</t>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 2</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 1</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>FTP
 PROF PUB 1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 4</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -5647,14 +5647,14 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
@@ -5673,15 +5673,15 @@
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/horario_gerado.xlsx
+++ b/outputs/horario_gerado.xlsx
@@ -60,7 +60,7 @@
       <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -79,12 +79,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4B183"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EADCF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D18E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -161,8 +186,23 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -584,8 +624,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 1</t>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -595,20 +635,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>GEO
-PROF GEO 3</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 1</t>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF ADM 1</t>
         </is>
       </c>
     </row>
@@ -616,44 +656,49 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF ADM 1</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
       <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 2</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
         </is>
       </c>
     </row>
@@ -661,44 +706,44 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF ADM 1</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 1</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 3</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
         </is>
       </c>
     </row>
@@ -706,21 +751,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>ING
 PROF ING 2</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -728,7 +768,7 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
@@ -736,11 +776,11 @@
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
@@ -811,10 +851,10 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 3</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -822,22 +862,22 @@
           <t>PROJ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>HIS
 PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
         </is>
       </c>
     </row>
@@ -845,49 +885,49 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 1</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 3</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF MMD 1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 1</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
         </is>
       </c>
     </row>
@@ -895,39 +935,39 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 3</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 2</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 3</t>
         </is>
       </c>
     </row>
@@ -935,16 +975,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -952,23 +992,23 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D5:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1034,10 +1074,10 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 2</t>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF MMD 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1045,22 +1085,22 @@
           <t>PROJ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 1</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 3</t>
         </is>
       </c>
     </row>
@@ -1068,106 +1108,106 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 1</t>
-        </is>
-      </c>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 3</t>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>ART
 PROF ART 1</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 1</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 2</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 3</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1175,22 +1215,22 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1257,33 +1297,33 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 3</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 1</t>
         </is>
       </c>
     </row>
@@ -1291,34 +1331,44 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 3</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 2</t>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF MMD 1</t>
         </is>
       </c>
     </row>
@@ -1326,71 +1376,61 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 1</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>ART
 PROF ART 1</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 3</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1398,22 +1438,22 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="F5:F8"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1482,28 +1522,28 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
           <t>FTP
 PROF MMD 2</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 3</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>ART
 PROF ART 1</t>
@@ -1514,11 +1554,11 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
@@ -1529,24 +1569,24 @@
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>HIS
 PROF HIS 1</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 4</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 4</t>
         </is>
       </c>
     </row>
@@ -1554,49 +1594,49 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 3</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 3</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 3</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 3</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 3</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 4</t>
         </is>
       </c>
     </row>
@@ -1604,16 +1644,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1621,23 +1661,23 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D6"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1703,33 +1743,33 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 4</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF MMD 2</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
         </is>
       </c>
     </row>
@@ -1737,19 +1777,14 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>SOC
-PROF SOC 2</t>
+          <t>FIS
+PROF FIS 1</t>
         </is>
       </c>
     </row>
@@ -1757,86 +1792,91 @@
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 3</t>
         </is>
       </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 1</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>EDF
 PROF EDF 4</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 2</t>
-        </is>
-      </c>
+      <c r="F7" s="9" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1844,22 +1884,22 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B3:B6"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F6:F7"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1926,10 +1966,10 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1943,13 +1983,13 @@
 PROF QUI 4</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF MMD 3</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 3</t>
@@ -1960,36 +2000,36 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 4</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>FIS
 PROF FIS 3</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF MMD 3</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>HIS
 PROF HIS 1</t>
@@ -2000,11 +2040,16 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
@@ -2015,26 +2060,26 @@
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 3</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 4</t>
@@ -2045,21 +2090,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 3</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2067,22 +2107,22 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2149,33 +2189,33 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 3</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 4</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
         </is>
       </c>
     </row>
@@ -2183,46 +2223,36 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 4</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 4</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 4</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF MMD 3</t>
@@ -2233,11 +2263,16 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -2245,44 +2280,49 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 4</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 4</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>ART
 PROF ART 2</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 3</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 1</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>ING
 PROF ING 2</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2290,22 +2330,22 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B4:B5"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F8"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2372,33 +2412,33 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 4</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 4</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 4</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 4</t>
         </is>
       </c>
     </row>
@@ -2406,39 +2446,39 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF MMD 3</t>
         </is>
       </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 4</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 3</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
         </is>
       </c>
     </row>
@@ -2446,39 +2486,44 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 4</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 4</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>HIS
 PROF HIS 1</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 4</t>
         </is>
       </c>
     </row>
@@ -2486,26 +2531,21 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
+      <c r="B8" s="9" t="n"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2513,23 +2553,23 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B8"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D5:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2595,33 +2635,33 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF TI 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 5</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 5</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 2</t>
         </is>
       </c>
     </row>
@@ -2629,44 +2669,44 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF TI 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
+          <t>QUI
+PROF QUI 2</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 2</t>
         </is>
       </c>
     </row>
@@ -2674,41 +2714,46 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 5</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>EDF
 PROF EDF 2</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 1</t>
@@ -2719,16 +2764,11 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2736,23 +2776,23 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B3:B6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2818,33 +2858,33 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 5</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 2</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 5</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
     </row>
@@ -2852,19 +2892,14 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 2</t>
         </is>
       </c>
     </row>
@@ -2874,42 +2909,37 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
+          <t>QUI
+PROF QUI 2</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF TI 1</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
     </row>
@@ -2919,27 +2949,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 5</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 2</t>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 2</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
         </is>
       </c>
     </row>
@@ -2947,11 +2977,21 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2959,21 +2999,21 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D8"/>
   </mergeCells>
@@ -3041,10 +3081,10 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 3</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3052,22 +3092,22 @@
           <t>PROJ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF ADM 1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
         </is>
       </c>
     </row>
@@ -3075,44 +3115,44 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 2</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 2</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF ADM 1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 1</t>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -3120,44 +3160,44 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 3</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>BIO
 PROF BIO 2</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF ADM 1</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
         </is>
       </c>
     </row>
@@ -3165,21 +3205,21 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 2</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 1</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3187,21 +3227,21 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
@@ -3270,33 +3310,33 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>EDF
 PROF EDF 2</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 1</t>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 5</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF TI 1</t>
+          <t>FIS
+PROF FIS 2</t>
         </is>
       </c>
     </row>
@@ -3304,84 +3344,79 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 5</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 2</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF TI 1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 2</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 2</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 5</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>ART
 PROF ART 1</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 5</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
+      <c r="E7" s="8" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 5</t>
+          <t>BIO
+PROF BIO 1</t>
         </is>
       </c>
     </row>
@@ -3389,19 +3424,24 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>ING
 PROF ING 1</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
         </is>
       </c>
     </row>
@@ -3411,21 +3451,21 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F3:F6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E5:E8"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
@@ -3493,33 +3533,33 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 2</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 6</t>
         </is>
       </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 4</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 6</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 6</t>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF TI 2</t>
         </is>
       </c>
     </row>
@@ -3527,84 +3567,84 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF TI 2</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="8" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 3</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 2</t>
-        </is>
-      </c>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 2</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 4</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 2</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 2</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 6</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 6</t>
         </is>
       </c>
     </row>
@@ -3612,21 +3652,21 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3634,23 +3674,23 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3716,10 +3756,10 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 6</t>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 2</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3727,22 +3767,22 @@
           <t>PROJ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 6</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF TI 2</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 3</t>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 6</t>
         </is>
       </c>
     </row>
@@ -3750,39 +3790,49 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 4</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 2</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF TI 2</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 2</t>
         </is>
       </c>
     </row>
@@ -3790,49 +3840,39 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 2</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 3</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>EDF
-PROF EDF 2</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 6</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 6</t>
-        </is>
-      </c>
+      <c r="E7" s="8" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>HIS
-PROF HIS 2</t>
+          <t>QUI
+PROF QUI 2</t>
         </is>
       </c>
     </row>
@@ -3840,16 +3880,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3857,23 +3897,23 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E5:E8"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3939,7 +3979,7 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 6</t>
@@ -3950,22 +3990,22 @@
           <t>PROJ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 6</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 4</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 6</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 2</t>
         </is>
       </c>
     </row>
@@ -3973,39 +4013,39 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 2</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF TI 2</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 1</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 3</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 2</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
         </is>
       </c>
     </row>
@@ -4013,66 +4053,66 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 2</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 1</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 6</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 6</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 2</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>HIS
 PROF HIS 2</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 1</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 1</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 1</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 6</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4080,23 +4120,23 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="B5:B8"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4164,31 +4204,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 2</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
           <t>FTP
 PROF ADM 1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 2</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
         </is>
       </c>
     </row>
@@ -4196,11 +4236,11 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4208,24 +4248,24 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>FIS
+PROF FIS 1</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
           <t>MAT
 PROF MAT 1</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>ART
 PROF ART 2</t>
@@ -4236,16 +4276,16 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 2</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>ING
 PROF ING 2</t>
@@ -4256,34 +4296,34 @@
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF ADM 1</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 1</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 3</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 1</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF ADM 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 3</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -4291,16 +4331,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 1</t>
-        </is>
-      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4308,12 +4348,13 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
@@ -4322,10 +4363,9 @@
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4391,10 +4431,10 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 3</t>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4402,22 +4442,22 @@
           <t>PROJ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 2</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF GSD 1</t>
         </is>
       </c>
     </row>
@@ -4425,44 +4465,44 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>HIS
 PROF HIS 2</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF GSD 1</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>FIS
 PROF FIS 2</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
         </is>
       </c>
     </row>
@@ -4470,49 +4510,54 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 1</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 2</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 5</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 3</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF GSD 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 5</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 2</t>
         </is>
       </c>
     </row>
@@ -4520,16 +4565,11 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4537,7 +4577,7 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4546,15 +4586,15 @@
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4620,10 +4660,10 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4631,22 +4671,22 @@
           <t>PROJ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 4</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF IA 1</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
     </row>
@@ -4656,14 +4696,24 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 1</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="5" t="n"/>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -4671,39 +4721,34 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 3</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>GEO
 PROF GEO 1</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -4711,32 +4756,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 7</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 1</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 3</t>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 7</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 4</t>
         </is>
       </c>
     </row>
@@ -4744,16 +4789,11 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4761,23 +4801,23 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F3:F6"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4843,33 +4883,33 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 3</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF IA 1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 7</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 7</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
         </is>
       </c>
     </row>
@@ -4877,89 +4917,89 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 3</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF IA 1</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 4</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 1</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 4</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 3</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FIS
-PROF FIS 3</t>
+          <t>QUI
+PROF QUI 3</t>
         </is>
       </c>
     </row>
@@ -4967,16 +5007,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 1</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4984,22 +5024,22 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5066,33 +5106,33 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FIS
+PROF FIS 3</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>FIL
 PROF FIL 4</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PROJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF IA 1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 3</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 3</t>
         </is>
       </c>
     </row>
@@ -5100,84 +5140,89 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="8" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 1</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 4</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 3</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 7</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 3</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>BIO
 PROF BIO 1</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 1</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 7</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 4</t>
         </is>
       </c>
     </row>
@@ -5185,21 +5230,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 4</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5207,23 +5247,23 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="F3:F6"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5289,10 +5329,10 @@
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5300,22 +5340,22 @@
           <t>PROJ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>ART
-PROF ART 2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>FTP
 PROF PUB 1</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 4</t>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
         </is>
       </c>
     </row>
@@ -5323,64 +5363,59 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ING
-PROF ING 2</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>QUI
+PROF QUI 1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 2</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF PUB 1</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>SOC
 PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>BIO
+PROF BIO 2</t>
         </is>
       </c>
     </row>
@@ -5388,34 +5423,34 @@
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>QUI
-PROF QUI 1</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 4</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ART
+PROF ART 2</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>MAT
 PROF MAT 2</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 2</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF PUB 1</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FIL
-PROF FIL 1</t>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
     </row>
@@ -5423,11 +5458,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ING
+PROF ING 2</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5435,23 +5475,23 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5520,8 +5560,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FTP
-PROF PUB 1</t>
+          <t>FIS
+PROF FIS 3</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5529,22 +5569,22 @@
           <t>PROJ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FIL
-PROF FIL 1</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>HIS
+PROF HIS 3</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>MAT
-PROF MAT 2</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MAT
-PROF MAT 2</t>
+          <t>BIO
+PROF BIO 2</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>EDF
+PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -5552,11 +5592,21 @@
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>SOC
+PROF SOC 1</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>POR
+PROF POR 2</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -5564,24 +5614,24 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>POR
-PROF POR 2</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>HIS
-PROF HIS 3</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
           <t>QUI
 PROF QUI 1</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>GEO
+PROF GEO 4</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>POR
 PROF POR 2</t>
@@ -5592,54 +5642,44 @@
       <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>BIO
-PROF BIO 2</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>SOC
-PROF SOC 1</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>MAT
+PROF MAT 2</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF PUB 1</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>FIL
+PROF FIL 1</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>FTP
+PROF PUB 1</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>ART
 PROF ART 2</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>FTP
-PROF PUB 1</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>GEO
-PROF GEO 4</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FIS
-PROF FIS 3</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>EDF
-PROF EDF 1</t>
         </is>
       </c>
     </row>
@@ -5647,16 +5687,16 @@
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>ING
 PROF ING 2</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5664,7 +5704,7 @@
           <t>Aulas ocupadas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>30</v>
       </c>
     </row>
@@ -5673,15 +5713,15 @@
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
